--- a/astro-site/public/dl/plan-negocio-cafeteria-movil-eventos/plan-financiero-cafeteria-movil-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-cafeteria-movil-eventos/plan-financiero-cafeteria-movil-eventos.xlsx
@@ -823,8 +823,8 @@
         <v>6.820000000000001</v>
       </c>
       <c r="C9" t="str">
-        <f>IFERROR("Precio por invitado sin IVA más el IVA medio ponderado de tus líneas de venta: "&amp;TEXT(SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)*100,"0")&amp;" %. Todo lo que sirve la cafetería móvil va al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992), en la barra del evento y en la venta directa de ferias y mercados: el precio con IVA es el de sin IVA por 1,10. Aquí va redondeado. Compáralo con el rango del sector, que va con IVA.","")</f>
-        <v>Precio por invitado sin IVA más el IVA medio ponderado de tus líneas de venta: 10 %. Todo lo que sirve la cafetería móvil va al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992), en la barra del evento y en la venta directa de ferias y mercados: el precio con IVA es el de sin IVA por 1,10. Aquí va redondeado. Compáralo con el rango del sector, que va con IVA.</v>
+        <f>IFERROR("Precio por invitado sin IVA más el IVA medio ponderado de tus líneas de venta: "&amp;TEXT(SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)*100,"0")&amp;" %. Todo lo que sirve la cafetería, en la barra o en la venta directa, va al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992). Aquí va redondeado. Compáralo con el precio por invitado de las barras de tu zona, que suele ir con IVA.","")</f>
+        <v>Precio por invitado sin IVA más el IVA medio ponderado de tus líneas de venta: 10 %. Todo lo que sirve la cafetería, en la barra o en la venta directa, va al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992). Aquí va redondeado. Compáralo con el precio por invitado de las barras de tu zona, que suele ir con IVA.</v>
       </c>
     </row>
     <row r="10">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cuota del almacén base: una nave o un garaje con fregadero y punto de agua donde se lavan la loza, las jarras y los depósitos, se guardan el café, la leche y los vasos, y duerme la furgoneta. No hay cocina ni se elabora comida; la casa o un trastero sin agua no sirven (RD 1021/2022, art. 13.5.b). Pide dos presupuestos en tu zona</t>
+          <t>Cuota del almacén base: una nave o un garaje con fregadero y punto de agua donde se lavan la loza, las jarras y los depósitos, se guardan el café, la leche y los vasos, y duerme la furgoneta. No hay cocina ni se elabora comida: no se prepara nada en casa para un evento (RD 1021/2022, art. 13.5.b), y un trastero sin agua no sirve para lavar loza ni depósitos. Pide dos presupuestos en tu zona</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Una cafetería móvil que arranca factura poco el primer mes: el café se contrata después que la finca y el catering, con uno a seis meses de antelación, y las empresas tardan en repetir. Con 100 % se elimina la rampa</t>
+          <t>Una cafetería móvil que arranca factura poco el primer mes: el café se contrata después que la finca y el catering, de una semana a seis meses antes, y las empresas tardan en repetir. Con 100 % se elimina la rampa</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Media ponderada: los particulares (bodas y celebraciones) pagan el 30 % de señal al firmar y el 70 % siete días antes del evento, y la venta directa se cobra en el momento; las empresas, agencias y congresos, el 52 % de las ventas, pagan el 30 % al confirmar y el 70 % a 30 días de la factura (contrato y calculadora del kit). El libro no admite días negativos, así que las señales no se modelan: tu caja real será algo MEJOR que la de la hoja de Tesorería</t>
+          <t>Media ponderada: los particulares (bodas y celebraciones) pagan el 30 % de señal al firmar y el 70 % siete días antes del evento, y la venta directa se cobra en el momento; las empresas, agencias y congresos, la mitad de las ventas, pagan el 30 % al confirmar y el 70 % a 30 días de la factura (contrato y calculadora del kit). El libro no admite días negativos, así que las señales no se modelan: tu caja real será algo MEJOR que la de la hoja de Tesorería</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>Furgoneta de ocasión tipo Kangoo L2 o Trafic (12.000-16.000 € en el mercado; el caso, 14.000 €) con la rotulación de la marca, estanterías y anclajes para llevar la barra, la cafetera y los depósitos sujetos. Si fijas en ella fregadero, depósitos o mueble, es una reforma de vehículo: informe de conformidad e ITV. Estimación del kit</t>
+          <t>Furgoneta de ocasión tipo Kangoo L2 o Trafic (12.000-16.000 € en el mercado; el caso, 14.000 €) con la rotulación de la marca, estanterías y anclajes para llevar la barra, la cafetera y los depósitos sujetos. Si fijas en ella fregadero, depósitos o mueble, es una reforma de vehículo: informe de conformidad e ITV. Estimación del kit. Si la compras a un particular no hay IVA, sino el impuesto de transmisiones; en un concesionario, en REBU, el IVA no se deduce: pon «No» en la columna de al lado</t>
         </is>
       </c>
       <c r="E7" s="31" t="inlineStr">
@@ -2080,8 +2080,8 @@
         <v>0.013319879145406542</v>
       </c>
       <c r="D21" s="28" t="str">
-        <f>IFERROR(""&amp;TEXT('0. Supuestos'!$B$25,"0")&amp;" meses de renta, al tipo de la hoja de Supuestos. Es un activo recuperable al cerrar: ni se amortiza ni lleva IVA","")</f>
-        <v>2 meses de renta, al tipo de la hoja de Supuestos. Es un activo recuperable al cerrar: ni se amortiza ni lleva IVA</v>
+        <f>IFERROR(""&amp;TEXT('0. Supuestos'!$B$25,"0")&amp;" cuotas del almacén base, al tipo de la hoja de Supuestos. Es un activo recuperable al cerrar: ni se amortiza ni lleva IVA","")</f>
+        <v>2 cuotas del almacén base, al tipo de la hoja de Supuestos. Es un activo recuperable al cerrar: ni se amortiza ni lleva IVA</v>
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
@@ -2104,8 +2104,8 @@
         <v>0.006659939572703271</v>
       </c>
       <c r="D22" s="28" t="str">
-        <f>IFERROR("Renta "&amp;IF('0. Supuestos'!$B$54=1,"del mes","de los "&amp;TEXT('0. Supuestos'!$B$54,"0")&amp;" meses")&amp;" de puesta en marcha (pruebas de carta, catas y primeras reservas). NO se solapa con el P&amp;L, que arranca el día de la apertura: los doce meses del P&amp;L son los doce de explotación","")</f>
-        <v>Renta del mes de puesta en marcha (pruebas de carta, catas y primeras reservas). NO se solapa con el P&amp;L, que arranca el día de la apertura: los doce meses del P&amp;L son los doce de explotación</v>
+        <f>IFERROR("Cuota "&amp;IF('0. Supuestos'!$B$54=1,"del mes","de los "&amp;TEXT('0. Supuestos'!$B$54,"0")&amp;" meses")&amp;" de puesta en marcha (montaje del almacén, calibrado de la cafetera, catas y primeras reservas). NO se solapa con el P&amp;L, que arranca el día de la apertura: los doce meses del P&amp;L son los doce de explotación","")</f>
+        <v>Cuota del mes de puesta en marcha (montaje del almacén, calibrado de la cafetera, catas y primeras reservas). NO se solapa con el P&amp;L, que arranca el día de la apertura: los doce meses del P&amp;L son los doce de explotación</v>
       </c>
       <c r="E22" s="28" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="F35" s="28" t="inlineStr">
         <is>
-          <t>Autorizaciones municipales de venta no sedentaria y tasas de ocupación de las jornadas de venta directa (RD 199/2010). Las tasas no llevan IVA. Pon las de tu ayuntamiento</t>
+          <t>Autorizaciones municipales de venta no sedentaria y tasas de ocupación de las jornadas de venta directa (RD 199/2010). Pon las de tu ayuntamiento. Las tasas municipales no llevan IVA, pero el libro aplica a todos los costes fijos el tipo general de la columna de al lado: aquí suma unos 63 € al año de IVA que pagas y te deduces en el mismo trimestre, sin efecto en el resultado</t>
         </is>
       </c>
       <c r="G35" s="68">
@@ -5660,7 +5660,7 @@
     <row r="7">
       <c r="A7" s="28" t="inlineStr">
         <is>
-          <t>Suplencias de vacaciones y bajas (fijo discontinuo)</t>
+          <t>Suplencias y refuerzo de temporada (fijo discontinuo)</t>
         </is>
       </c>
       <c r="B7" s="49" t="n">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="J7" s="28" t="inlineStr">
         <is>
-          <t>Bolsa para cubrir las vacaciones y las bajas del camarero/a en temporada: unas 75 horas al año, mismo contrato y misma categoría. Nunca como autónomo que te factura: con tu horario y tu dirección es falso autónomo (art. 1.1 del Estatuto de los Trabajadores)</t>
+          <t>Bolsa para cubrir las vacaciones del camarero/a y los picos de temporada: unas 75 horas al año, mismo contrato y misma categoría. Para cubrir una baja concreta, el contrato es de sustitución (art. 15.3 del Estatuto de los Trabajadores). Nunca como autónomo que te factura: con tu horario y tu dirección es falso autónomo (art. 1.1)</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6610,7 @@
       </c>
       <c r="D35" s="46" t="inlineStr">
         <is>
-          <t>El café se reserva con uno a seis meses de antelación: se arranca en primavera, con la empresa y las comuniones, y enero y febrero (los meses más flojos) llegan con la caja de la temporada. La fila de estacionalidad de la Tesorería ya va girada</t>
+          <t>El café se reserva de una semana a seis meses antes: se arranca en primavera, con la empresa y las comuniones, y enero y febrero (los meses más flojos) llegan con la caja de la temporada. La fila de estacionalidad de la Tesorería ya va girada</t>
         </is>
       </c>
       <c r="E35" s="28" t="n"/>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="E44" s="28" t="n"/>
     </row>
-    <row r="45" ht="60" customHeight="1">
+    <row r="45" ht="75" customHeight="1">
       <c r="A45" s="28" t="inlineStr">
         <is>
           <t>Cobro y cancelación del kit</t>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="D45" s="46" t="inlineStr">
         <is>
-          <t>Cancelación en cuatro tramos (particular: 60, 30 y 7 días; empresa: 30, 15 y 7): se retiene el 10, el 30, el 60 o el 100 % del precio, menos los costes que te ahorras; recíproca si cancelas tú. En la feria se cobra en el acto</t>
+          <t>Cancelación en cuatro tramos (particular: 60, 30 y 7 días; empresa: 30, 15 y 7): se retiene el 10, el 30 o el 60 % del precio, y en el último tramo el 100 % menos los costes que te ahorras; recíproca si cancelas tú. En la feria se cobra en el acto</t>
         </is>
       </c>
       <c r="E45" s="28" t="n"/>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="E48" s="28" t="n"/>
     </row>
-    <row r="49" ht="60" customHeight="1">
+    <row r="49" ht="75" customHeight="1">
       <c r="A49" s="28" t="inlineStr">
         <is>
           <t>Comida testigo</t>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="D49" s="46" t="inlineStr">
         <is>
-          <t>Una ración de 100 g o más durante 7 días, en cada evento. Según nuestra lectura, las bebidas y la bollería servida tal cual quedan fuera, sin criterio oficial: confírmalo con tu autoridad sanitaria</t>
+          <t>Una ración de 100 g o más, a 4 °C o menos (o congelada), durante 7 días, en cada evento. Según nuestra lectura, las bebidas y la bollería servida tal cual quedan fuera, sin criterio oficial: confírmalo con tu autoridad sanitaria</t>
         </is>
       </c>
       <c r="E49" s="28" t="n"/>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="O5" s="28" t="inlineStr">
         <is>
-          <t>Mes 1 = MARZO: el café se reserva con uno a seis meses de antelación y se arranca en primavera, con la empresa y las comuniones. Los picos son mayo y junio (Meses 3 y 4) y septiembre y octubre (Meses 7 y 8); el valle, agosto (Mes 6) y enero (Mes 11). Si arrancas en otro mes, gira la fila. Tiene que sumar 100 %</t>
+          <t>Mes 1 = MARZO: el café se reserva de una semana a seis meses antes y se arranca en primavera, con la empresa y las comuniones. Los picos son mayo y junio (Meses 3 y 4) y septiembre y octubre (Meses 7 y 8); el valle, agosto (Mes 6) y enero (Mes 11). Si arrancas en otro mes, gira la fila. Tiene que sumar 100 %</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-cafeteria-movil-eventos/plan-financiero-cafeteria-movil-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-cafeteria-movil-eventos/plan-financiero-cafeteria-movil-eventos.xlsx
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E28" s="28" t="n"/>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="25" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Marca, web, fotos y dossier, Constitución SL + notaría + registro, Declaración responsable, APPCC, alérgenos y formación de barista, Stock inicial: café, leche UHT y vasos, Lanzamiento: feria nupcial, escaparate de bodas y catas para agencias, Fianza del almacén base, Cuota del almacén base de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Marca, web, fotos y dossier, Constitución SL + notaría + registro, Declaración responsable, APPCC, alérgenos y formación de barista, Stock inicial: café, leche UHT y vasos, Lanzamiento: feria "&amp;"nupcial, escaparate de bodas y catas para agencias, Fianza del almacén base, Cuota del almacén base de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Marca, web, fotos y dossier, Constitución SL + notaría + registro, Declaración responsable, APPCC, alérgenos y formación de barista, Stock inicial: café, leche UHT y vasos, Lanzamiento: feria nupcial, escaparate de bodas y catas para agencias, Fianza del almacén base, Cuota del almacén base de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman 23145 € de los 60061 € de inversión.</v>
       </c>
       <c r="E33" s="28" t="n"/>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>

--- a/astro-site/public/dl/plan-negocio-cafeteria-movil-eventos/plan-financiero-cafeteria-movil-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-cafeteria-movil-eventos/plan-financiero-cafeteria-movil-eventos.xlsx
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-cafeteria-movil-eventos/plan-financiero-cafeteria-movil-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-cafeteria-movil-eventos/plan-financiero-cafeteria-movil-eventos.xlsx
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E28" s="28" t="n"/>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="25" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Marca, web, fotos y dossier, Constitución SL + notaría + registro, Declaración responsable, APPCC, alérgenos y formación de barista, Stock inicial: café, leche UHT y vasos, Lanzamiento: feria nupcial, escaparate de bodas y catas para agencias, Fianza del almacén base, Cuota del almacén base de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Marca, web, fotos y dossier, Constitución SL + notaría + registro, Declaración responsable, APPCC, alérgenos y formación de barista, Stock inicial: café, leche UHT y vasos, Lanzamiento: feria "&amp;"nupcial, escaparate de bodas y catas para agencias, Fianza del almacén base, Cuota del almacén base de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Marca, web, fotos y dossier, Constitución SL + notaría + registro, Declaración responsable, APPCC, alérgenos y formación de barista, Stock inicial: café, leche UHT y vasos, Lanzamiento: feria nupcial, escaparate de bodas y catas para agencias, Fianza del almacén base, Cuota del almacén base de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman 23145 € de los 60061 € de inversión.</v>
       </c>
       <c r="E33" s="28" t="n"/>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>
